--- a/arena_data.xlsx
+++ b/arena_data.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amit\Desktop\MyProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDD5EA6-7410-430E-9503-9E1B2C0C22D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFD9B79-8CB0-46A1-A721-98106C85C29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F76FAD0E-8443-4B80-95DE-0037496B47B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$355</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,187 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="562">
-  <si>
-    <t>MARUTI ERTIGA VXI CNG 1.5L 5MT BS-VI</t>
-  </si>
-  <si>
-    <t>MARUTI WAGON R ZXI+ 1.2L ISS 5MT-WAR4KZ2</t>
-  </si>
-  <si>
-    <t>MARUTI TOUR S CNG 1.2L 5MT-DERCAT1</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE LXI 1.2L ISS 5MT-DER4AL1</t>
-  </si>
-  <si>
-    <t>MARUTI ERTIGA ZXI CNG 1.5L 5MT-ERRCIZ1</t>
-  </si>
-  <si>
-    <t>MARUTI VICTORIS VXI CNG 1.5L 5MT-ECRCAV1</t>
-  </si>
-  <si>
-    <t>MARUTI EECO 6 STR STD 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE VXI 1.2L ISS 5MT BSVI-</t>
-  </si>
-  <si>
-    <t>MARUTI EECO 5 STR AC CNG 1.2L 5MT BSVI</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT VXI CNG 1.2L 5MT-SIRCAV1</t>
-  </si>
-  <si>
-    <t>MARUTI WAGON R VXI CNG 1L 5MT-WARCKV1</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA VXI 1.5L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE VXI CNG 1.2L 5MT BS-VI</t>
-  </si>
-  <si>
-    <t>MARUTI VICTORIS LXI CNG 1.5L 5MT-ECRCAL1</t>
-  </si>
-  <si>
-    <t>MARUTI WAGON R LXI 1L ISS 5MT-WAR4KL1</t>
-  </si>
-  <si>
-    <t>MARUTI WAGON R VXI 1L ISS AGS-WAA4KV1</t>
-  </si>
-  <si>
-    <t>MARUTI WAGON R VXI 1L ISS 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE ZXI CNG 1.2L 5MT BS-VI</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA VXI CNG 1.5L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI VICTORIS VXI 1.5L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE ZXI ISS CNG 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE VXI ISS CNG 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI EECO AMBULANCE SHELL 1.2L 5MT-VRMPIA1</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA VXI TURBO 1.0L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI VICTORIS LXI 1.5L 5MT-ECR4AL1</t>
-  </si>
-  <si>
-    <t>MARUTI EECO 5 STR AC 1.2L 5MT.</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT VXI (O) CNG 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA ZXI CNG 1.5L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI ERTIGA SMART HYBRID VXI 1.5L 5MT-ERR4IV1</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA VXI 1.5L 6AT</t>
-  </si>
-  <si>
-    <t>MARUTI ALTO K10 VXI 1L 5MT-ATR4HV1</t>
-  </si>
-  <si>
-    <t>MARUTI VICTORIS ZXI CNG 1.5L 5MT-ECRCAZ1</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT LXI 1.2L ISS 5MT BSVI</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA LXI TURBO 1.0L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT VXI ISS CNG 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI TOUR S ISS CNG 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT VXI ISS 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT VXI 1.2L ISS 5MT BSVI</t>
-  </si>
-  <si>
-    <t>MARUTI SUPER CARRY STD CNG 1.2L 5MT-CARCGS2</t>
-  </si>
-  <si>
-    <t>MARUTI WAGON R VXI CNG 1L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT LXI ISS 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI WAGON R LXI CNG 1L 5MT-WARCKL1</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT VXI 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI VICTORIS ZXI(O) 1.5L 6AT-ECA4BZ1</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT VXI (O) ISS CNG 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE ZXI 1.2L ISS 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA ZXI 1.5L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE ZXI+ 1.2L ISS 5MT BS-VI</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE ZXI 1.2L ISS 5MT BS-VI</t>
-  </si>
-  <si>
-    <t>MARUTI SWIFT VXI (O) 1.2L ISS 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI ERTIGA ZXI CNG 1.5L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA LXI 1.5L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE LXI ISS 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE ZXI ISS 1.2L 5MT</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA ZXI TURBO 1.0L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA VXI CNG 1.5L 5MT.</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA VXI 1.5L 5MT-VZR4GV1</t>
-  </si>
-  <si>
-    <t>MARUTI ERTIGA VXI CNG 1.5L</t>
-  </si>
-  <si>
-    <t>MARUTI BREZZA LXI CNG 1.5L 6MT</t>
-  </si>
-  <si>
-    <t>MARUTI DZIRE ZXI ISS CNG 1.2L AGS</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="512">
   <si>
     <t>RAMJAN AHMAD-2670510184</t>
   </si>
@@ -1725,13 +1548,43 @@
   </si>
   <si>
     <t>SRM</t>
+  </si>
+  <si>
+    <t>ERTIGA</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>VICTORIS</t>
+  </si>
+  <si>
+    <t>EECO</t>
+  </si>
+  <si>
+    <t>SWIFT</t>
+  </si>
+  <si>
+    <t>BREZZA</t>
+  </si>
+  <si>
+    <t>WAGON R</t>
+  </si>
+  <si>
+    <t>TOUR S</t>
+  </si>
+  <si>
+    <t>SUPER CARRY</t>
+  </si>
+  <si>
+    <t>ALTO K10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1747,13 +1600,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1763,7 +1609,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1771,31 +1617,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2142,33 +1970,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>558</v>
+        <v>498</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>561</v>
+        <v>501</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>559</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>557</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>414</v>
+        <v>354</v>
       </c>
       <c r="C2" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -2176,16 +2004,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="C3" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>508</v>
       </c>
       <c r="E3">
         <v>29998</v>
@@ -2193,16 +2021,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>418</v>
+        <v>358</v>
       </c>
       <c r="C4" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="E4">
         <v>16303</v>
@@ -2210,16 +2038,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D5" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="E5">
         <v>16549</v>
@@ -2227,16 +2055,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>421</v>
+        <v>361</v>
       </c>
       <c r="C6" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>503</v>
       </c>
       <c r="E6">
         <v>21142</v>
@@ -2244,16 +2072,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="C7" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="E7">
         <v>10606</v>
@@ -2261,16 +2089,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>425</v>
+        <v>365</v>
       </c>
       <c r="C8" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D8" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -2278,16 +2106,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>427</v>
+        <v>367</v>
       </c>
       <c r="C9" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E9">
         <v>121590</v>
@@ -2295,16 +2123,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C10" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>505</v>
       </c>
       <c r="E10">
         <v>22444</v>
@@ -2312,16 +2140,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
       <c r="C11" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="E11">
         <v>15631</v>
@@ -2329,16 +2157,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="C12" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D12" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -2346,16 +2174,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D13" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2363,16 +2191,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="C14" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E14">
         <v>25785</v>
@@ -2380,16 +2208,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>436</v>
+        <v>376</v>
       </c>
       <c r="C15" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D15" t="s">
-        <v>8</v>
+        <v>505</v>
       </c>
       <c r="E15">
         <v>7932</v>
@@ -2397,16 +2225,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="C16" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>506</v>
       </c>
       <c r="E16">
         <v>20521</v>
@@ -2414,16 +2242,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>421</v>
+        <v>361</v>
       </c>
       <c r="C17" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E17">
         <v>26921</v>
@@ -2431,16 +2259,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="C18" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>507</v>
       </c>
       <c r="E18">
         <v>22758</v>
@@ -2448,16 +2276,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C19" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E19">
         <v>15890</v>
@@ -2465,16 +2293,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>441</v>
+        <v>381</v>
       </c>
       <c r="C20" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D20" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2482,16 +2310,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>442</v>
+        <v>382</v>
       </c>
       <c r="C21" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E21">
         <v>102241</v>
@@ -2499,16 +2327,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>443</v>
+        <v>383</v>
       </c>
       <c r="C22" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D22" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2516,16 +2344,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>444</v>
+        <v>384</v>
       </c>
       <c r="C23" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>508</v>
       </c>
       <c r="E23">
         <v>25000</v>
@@ -2533,16 +2361,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>441</v>
+        <v>381</v>
       </c>
       <c r="C24" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>508</v>
       </c>
       <c r="E24">
         <v>32000</v>
@@ -2550,16 +2378,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="C25" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E25">
         <v>28041</v>
@@ -2567,16 +2395,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="C26" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D26" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E26">
         <v>127248</v>
@@ -2584,16 +2412,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>445</v>
+        <v>385</v>
       </c>
       <c r="C27" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E27">
         <v>81484</v>
@@ -2601,16 +2429,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C28" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>503</v>
       </c>
       <c r="E28">
         <v>10825</v>
@@ -2618,16 +2446,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="C29" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E29">
         <v>30573</v>
@@ -2635,16 +2463,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
       <c r="C30" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E30">
         <v>20472</v>
@@ -2652,16 +2480,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>436</v>
+        <v>376</v>
       </c>
       <c r="C31" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>506</v>
       </c>
       <c r="E31">
         <v>21878</v>
@@ -2669,16 +2497,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="C32" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E32">
         <v>27894</v>
@@ -2686,16 +2514,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="C33" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E33">
         <v>6761</v>
@@ -2703,16 +2531,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="C34" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E34">
         <v>5000</v>
@@ -2720,16 +2548,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>448</v>
+        <v>388</v>
       </c>
       <c r="C35" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E35">
         <v>5000</v>
@@ -2737,16 +2565,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="C36" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>504</v>
       </c>
       <c r="E36">
         <v>106923</v>
@@ -2754,16 +2582,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="C37" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D37" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="E37">
         <v>15938</v>
@@ -2771,16 +2599,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>449</v>
+        <v>389</v>
       </c>
       <c r="C38" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D38" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="E38">
         <v>15000</v>
@@ -2788,16 +2616,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>444</v>
+        <v>384</v>
       </c>
       <c r="C39" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>503</v>
       </c>
       <c r="E39">
         <v>15507</v>
@@ -2805,16 +2633,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C40" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E40">
         <v>18709</v>
@@ -2822,16 +2650,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="C41" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>505</v>
       </c>
       <c r="E41">
         <v>4744</v>
@@ -2839,16 +2667,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="C42" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E42">
         <v>15662</v>
@@ -2856,16 +2684,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>452</v>
+        <v>392</v>
       </c>
       <c r="C43" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E43">
         <v>25826</v>
@@ -2873,16 +2701,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>454</v>
+        <v>394</v>
       </c>
       <c r="C44" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D44" t="s">
-        <v>8</v>
+        <v>505</v>
       </c>
       <c r="E44">
         <v>10516</v>
@@ -2890,16 +2718,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>455</v>
+        <v>395</v>
       </c>
       <c r="C45" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D45" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2907,16 +2735,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>456</v>
+        <v>396</v>
       </c>
       <c r="C46" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>507</v>
       </c>
       <c r="E46">
         <v>5579</v>
@@ -2924,16 +2752,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="C47" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E47">
         <v>117741</v>
@@ -2941,16 +2769,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>459</v>
+        <v>399</v>
       </c>
       <c r="C48" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>505</v>
       </c>
       <c r="E48">
         <v>21213</v>
@@ -2958,16 +2786,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="C49" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E49">
         <v>5866</v>
@@ -2975,16 +2803,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="C50" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E50">
         <v>29502</v>
@@ -2992,16 +2820,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>461</v>
+        <v>401</v>
       </c>
       <c r="C51" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D51" t="s">
-        <v>26</v>
+        <v>506</v>
       </c>
       <c r="E51">
         <v>15941</v>
@@ -3009,16 +2837,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>462</v>
+        <v>402</v>
       </c>
       <c r="C52" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E52">
         <v>30215</v>
@@ -3026,16 +2854,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>463</v>
+        <v>403</v>
       </c>
       <c r="C53" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D53" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E53">
         <v>5774</v>
@@ -3043,30 +2871,30 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>463</v>
+        <v>403</v>
       </c>
       <c r="C54" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D54" t="s">
-        <v>28</v>
+        <v>502</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>464</v>
+        <v>404</v>
       </c>
       <c r="C55" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E55">
         <v>5900</v>
@@ -3074,16 +2902,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>414</v>
+        <v>354</v>
       </c>
       <c r="C56" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>507</v>
       </c>
       <c r="E56">
         <v>25000</v>
@@ -3091,16 +2919,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>466</v>
+        <v>406</v>
       </c>
       <c r="C57" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D57" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3108,16 +2936,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>467</v>
+        <v>407</v>
       </c>
       <c r="C58" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D58" t="s">
-        <v>30</v>
+        <v>511</v>
       </c>
       <c r="E58">
         <v>29558</v>
@@ -3125,16 +2953,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="C59" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E59">
         <v>100340</v>
@@ -3142,16 +2970,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
       <c r="C60" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D60" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E60">
         <v>25754</v>
@@ -3159,16 +2987,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="C61" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E61">
         <v>30852</v>
@@ -3176,16 +3004,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C62" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>505</v>
       </c>
       <c r="E62">
         <v>21698</v>
@@ -3193,16 +3021,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C63" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E63">
         <v>123500</v>
@@ -3210,16 +3038,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>469</v>
+        <v>409</v>
       </c>
       <c r="C64" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D64" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E64">
         <v>25990</v>
@@ -3227,16 +3055,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="C65" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D65" t="s">
-        <v>26</v>
+        <v>506</v>
       </c>
       <c r="E65">
         <v>15990</v>
@@ -3244,16 +3072,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>471</v>
+        <v>411</v>
       </c>
       <c r="C66" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E66">
         <v>117577</v>
@@ -3261,16 +3089,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="C67" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D67" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E67">
         <v>5850</v>
@@ -3278,16 +3106,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>472</v>
+        <v>412</v>
       </c>
       <c r="C68" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E68">
         <v>30000</v>
@@ -3295,16 +3123,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>473</v>
+        <v>413</v>
       </c>
       <c r="C69" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D69" t="s">
-        <v>31</v>
+        <v>504</v>
       </c>
       <c r="E69">
         <v>140000</v>
@@ -3312,16 +3140,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>474</v>
+        <v>414</v>
       </c>
       <c r="C70" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D70" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3329,16 +3157,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>475</v>
+        <v>415</v>
       </c>
       <c r="C71" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D71" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3346,16 +3174,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>476</v>
+        <v>416</v>
       </c>
       <c r="C72" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D72" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -3363,16 +3191,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>478</v>
+        <v>418</v>
       </c>
       <c r="C73" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E73">
         <v>28339</v>
@@ -3380,16 +3208,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>479</v>
+        <v>419</v>
       </c>
       <c r="C74" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D74" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E74">
         <v>15900</v>
@@ -3397,16 +3225,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C75" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D75" t="s">
-        <v>23</v>
+        <v>507</v>
       </c>
       <c r="E75">
         <v>5000</v>
@@ -3414,16 +3242,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="C76" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E76">
         <v>29946</v>
@@ -3431,16 +3259,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="C77" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E77">
         <v>5000</v>
@@ -3448,16 +3276,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>481</v>
+        <v>421</v>
       </c>
       <c r="C78" t="s">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E78">
         <v>33186</v>
@@ -3465,16 +3293,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C79" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D79" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E79">
         <v>26943</v>
@@ -3482,16 +3310,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>456</v>
+        <v>396</v>
       </c>
       <c r="C80" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E80">
         <v>25803</v>
@@ -3499,16 +3327,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>461</v>
+        <v>401</v>
       </c>
       <c r="C81" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D81" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="E81">
         <v>15994</v>
@@ -3516,16 +3344,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="C82" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D82" t="s">
-        <v>33</v>
+        <v>507</v>
       </c>
       <c r="E82">
         <v>5000</v>
@@ -3533,16 +3361,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>483</v>
+        <v>423</v>
       </c>
       <c r="C83" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D83" t="s">
-        <v>34</v>
+        <v>506</v>
       </c>
       <c r="E83">
         <v>20481</v>
@@ -3550,16 +3378,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="C84" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D84" t="s">
-        <v>35</v>
+        <v>509</v>
       </c>
       <c r="E84">
         <v>15900</v>
@@ -3567,16 +3395,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C85" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D85" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E85">
         <v>116075</v>
@@ -3584,16 +3412,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="C86" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>506</v>
       </c>
       <c r="E86">
         <v>29912</v>
@@ -3601,16 +3429,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="C87" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E87">
         <v>33063</v>
@@ -3618,16 +3446,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="C88" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D88" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E88">
         <v>24122</v>
@@ -3635,16 +3463,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>485</v>
+        <v>425</v>
       </c>
       <c r="C89" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D89" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E89">
         <v>121890</v>
@@ -3652,16 +3480,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C90" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D90" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3669,16 +3497,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="C91" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E91">
         <v>31407</v>
@@ -3686,16 +3514,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>486</v>
+        <v>426</v>
       </c>
       <c r="C92" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D92" t="s">
-        <v>8</v>
+        <v>505</v>
       </c>
       <c r="E92">
         <v>11485</v>
@@ -3703,16 +3531,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>461</v>
+        <v>401</v>
       </c>
       <c r="C93" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D93" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E93">
         <v>109852</v>
@@ -3720,16 +3548,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
       <c r="C94" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D94" t="s">
-        <v>11</v>
+        <v>507</v>
       </c>
       <c r="E94">
         <v>15900</v>
@@ -3737,16 +3565,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>488</v>
+        <v>428</v>
       </c>
       <c r="C95" t="s">
-        <v>489</v>
+        <v>429</v>
       </c>
       <c r="D95" t="s">
-        <v>38</v>
+        <v>510</v>
       </c>
       <c r="E95">
         <v>29900</v>
@@ -3754,16 +3582,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>418</v>
+        <v>358</v>
       </c>
       <c r="C96" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D96" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E96">
         <v>117540</v>
@@ -3771,16 +3599,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>467</v>
+        <v>407</v>
       </c>
       <c r="C97" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D97" t="s">
-        <v>39</v>
+        <v>508</v>
       </c>
       <c r="E97">
         <v>26986</v>
@@ -3788,16 +3616,16 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="C98" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D98" t="s">
-        <v>40</v>
+        <v>506</v>
       </c>
       <c r="E98">
         <v>25851</v>
@@ -3805,16 +3633,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>483</v>
+        <v>423</v>
       </c>
       <c r="C99" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D99" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E99">
         <v>27610</v>
@@ -3822,16 +3650,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>483</v>
+        <v>423</v>
       </c>
       <c r="C100" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E100">
         <v>30943</v>
@@ -3839,16 +3667,16 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="C101" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D101" t="s">
-        <v>20</v>
+        <v>503</v>
       </c>
       <c r="E101">
         <v>16053</v>
@@ -3856,16 +3684,16 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="C102" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D102" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E102">
         <v>101672</v>
@@ -3873,16 +3701,16 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>483</v>
+        <v>423</v>
       </c>
       <c r="C103" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D103" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3890,16 +3718,16 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>471</v>
+        <v>411</v>
       </c>
       <c r="C104" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D104" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E104">
         <v>25992</v>
@@ -3907,16 +3735,16 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="C105" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D105" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E105">
         <v>26900</v>
@@ -3924,16 +3752,16 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="C106" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E106">
         <v>30970</v>
@@ -3941,16 +3769,16 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="C107" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D107" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3958,16 +3786,16 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>491</v>
+        <v>431</v>
       </c>
       <c r="C108" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D108" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E108">
         <v>27865</v>
@@ -3975,16 +3803,16 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>493</v>
+        <v>433</v>
       </c>
       <c r="C109" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D109" t="s">
-        <v>17</v>
+        <v>503</v>
       </c>
       <c r="E109">
         <v>15983</v>
@@ -3992,16 +3820,16 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="C110" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D110" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E110">
         <v>15987</v>
@@ -4009,16 +3837,16 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="C111" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D111" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E111">
         <v>126000</v>
@@ -4026,16 +3854,16 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="C112" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D112" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E112">
         <v>31725</v>
@@ -4043,16 +3871,16 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="C113" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D113" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E113">
         <v>15990</v>
@@ -4060,16 +3888,16 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="C114" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D114" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E114">
         <v>5859</v>
@@ -4077,16 +3905,16 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>498</v>
+        <v>438</v>
       </c>
       <c r="C115" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D115" t="s">
-        <v>8</v>
+        <v>505</v>
       </c>
       <c r="E115">
         <v>9990</v>
@@ -4094,16 +3922,16 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>427</v>
+        <v>367</v>
       </c>
       <c r="C116" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="D116" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E116">
         <v>5600</v>
@@ -4111,16 +3939,16 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>499</v>
+        <v>439</v>
       </c>
       <c r="C117" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D117" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E117">
         <v>15998</v>
@@ -4128,16 +3956,16 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="C118" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D118" t="s">
-        <v>9</v>
+        <v>506</v>
       </c>
       <c r="E118">
         <v>20000</v>
@@ -4145,16 +3973,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>499</v>
+        <v>439</v>
       </c>
       <c r="C119" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D119" t="s">
-        <v>8</v>
+        <v>505</v>
       </c>
       <c r="E119">
         <v>13465</v>
@@ -4162,16 +3990,16 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>499</v>
+        <v>439</v>
       </c>
       <c r="C120" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D120" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E120">
         <v>5957</v>
@@ -4179,16 +4007,16 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="C121" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E121">
         <v>30000</v>
@@ -4196,16 +4024,16 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="C122" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D122" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E122">
         <v>28304</v>
@@ -4213,16 +4041,16 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="C123" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D123" t="s">
-        <v>41</v>
+        <v>508</v>
       </c>
       <c r="E123">
         <v>25917</v>
@@ -4230,16 +4058,16 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>502</v>
+        <v>442</v>
       </c>
       <c r="C124" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D124" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E124">
         <v>24624</v>
@@ -4247,16 +4075,16 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>502</v>
+        <v>442</v>
       </c>
       <c r="C125" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D125" t="s">
-        <v>14</v>
+        <v>508</v>
       </c>
       <c r="E125">
         <v>30000</v>
@@ -4264,16 +4092,16 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>504</v>
+        <v>444</v>
       </c>
       <c r="C126" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D126" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E126">
         <v>22683</v>
@@ -4281,16 +4109,16 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>504</v>
+        <v>444</v>
       </c>
       <c r="C127" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D127" t="s">
-        <v>42</v>
+        <v>506</v>
       </c>
       <c r="E127">
         <v>23921</v>
@@ -4298,16 +4126,16 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>506</v>
+        <v>446</v>
       </c>
       <c r="C128" t="s">
+        <v>443</v>
+      </c>
+      <c r="D128" t="s">
         <v>503</v>
-      </c>
-      <c r="D128" t="s">
-        <v>7</v>
       </c>
       <c r="E128">
         <v>21999</v>
@@ -4315,16 +4143,16 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>187</v>
+        <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>507</v>
+        <v>447</v>
       </c>
       <c r="C129" t="s">
+        <v>448</v>
+      </c>
+      <c r="D129" t="s">
         <v>508</v>
-      </c>
-      <c r="D129" t="s">
-        <v>16</v>
       </c>
       <c r="E129">
         <v>24990</v>
@@ -4332,16 +4160,16 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>509</v>
+        <v>449</v>
       </c>
       <c r="C130" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D130" t="s">
-        <v>6</v>
+        <v>505</v>
       </c>
       <c r="E130">
         <v>24999</v>
@@ -4349,16 +4177,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="C131" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D131" t="s">
-        <v>14</v>
+        <v>508</v>
       </c>
       <c r="E131">
         <v>29308</v>
@@ -4366,16 +4194,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>507</v>
+        <v>447</v>
       </c>
       <c r="C132" t="s">
-        <v>508</v>
+        <v>448</v>
       </c>
       <c r="D132" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E132">
         <v>25795</v>
@@ -4383,16 +4211,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="C133" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D133" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4400,16 +4228,16 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>512</v>
+        <v>452</v>
       </c>
       <c r="C134" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E134">
         <v>28695</v>
@@ -4417,16 +4245,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>509</v>
+        <v>449</v>
       </c>
       <c r="C135" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D135" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4434,16 +4262,16 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>514</v>
+        <v>454</v>
       </c>
       <c r="C136" t="s">
-        <v>508</v>
+        <v>448</v>
       </c>
       <c r="D136" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E136">
         <v>24900</v>
@@ -4451,16 +4279,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>515</v>
+        <v>455</v>
       </c>
       <c r="C137" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D137" t="s">
-        <v>43</v>
+        <v>504</v>
       </c>
       <c r="E137">
         <v>134784</v>
@@ -4468,16 +4296,16 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="C138" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D138" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="E138">
         <v>14908</v>
@@ -4485,16 +4313,16 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>516</v>
+        <v>456</v>
       </c>
       <c r="C139" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D139" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E139">
         <v>22446</v>
@@ -4502,16 +4330,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>517</v>
+        <v>457</v>
       </c>
       <c r="C140" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D140" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E140">
         <v>26999</v>
@@ -4519,16 +4347,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>506</v>
+        <v>446</v>
       </c>
       <c r="C141" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D141" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4536,16 +4364,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>506</v>
+        <v>446</v>
       </c>
       <c r="C142" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D142" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4553,16 +4381,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>517</v>
+        <v>457</v>
       </c>
       <c r="C143" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D143" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E143">
         <v>28795</v>
@@ -4570,16 +4398,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="C144" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D144" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E144">
         <v>24789</v>
@@ -4587,16 +4415,16 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="C145" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D145" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E145">
         <v>15960</v>
@@ -4604,16 +4432,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>518</v>
+        <v>458</v>
       </c>
       <c r="C146" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D146" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E146">
         <v>119964</v>
@@ -4621,16 +4449,16 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>519</v>
+        <v>459</v>
       </c>
       <c r="C147" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D147" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E147">
         <v>16646</v>
@@ -4638,16 +4466,16 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>519</v>
+        <v>459</v>
       </c>
       <c r="C148" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D148" t="s">
-        <v>14</v>
+        <v>508</v>
       </c>
       <c r="E148">
         <v>30000</v>
@@ -4655,16 +4483,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>207</v>
+        <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>464</v>
+        <v>404</v>
       </c>
       <c r="C149" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D149" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E149">
         <v>8545</v>
@@ -4672,16 +4500,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>208</v>
+        <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>518</v>
+        <v>458</v>
       </c>
       <c r="C150" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D150" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E150">
         <v>99787</v>
@@ -4689,16 +4517,16 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>209</v>
+        <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>517</v>
+        <v>457</v>
       </c>
       <c r="C151" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D151" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E151">
         <v>29974</v>
@@ -4706,16 +4534,16 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="C152" t="s">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="D152" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -4723,16 +4551,16 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>211</v>
+        <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="C153" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D153" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E153">
         <v>78628</v>
@@ -4740,16 +4568,16 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C154" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D154" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E154">
         <v>15982</v>
@@ -4757,16 +4585,16 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C155" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D155" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -4774,16 +4602,16 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="C156" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D156" t="s">
-        <v>23</v>
+        <v>507</v>
       </c>
       <c r="E156">
         <v>7282</v>
@@ -4791,16 +4619,16 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>525</v>
+        <v>465</v>
       </c>
       <c r="C157" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D157" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -4808,16 +4636,16 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="C158" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D158" t="s">
-        <v>44</v>
+        <v>506</v>
       </c>
       <c r="E158">
         <v>15980</v>
@@ -4825,16 +4653,16 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="C159" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D159" t="s">
-        <v>45</v>
+        <v>503</v>
       </c>
       <c r="E159">
         <v>30980</v>
@@ -4842,16 +4670,16 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="C160" t="s">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="D160" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E160">
         <v>31947</v>
@@ -4859,16 +4687,16 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C161" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D161" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -4876,16 +4704,16 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="C162" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E162">
         <v>30980</v>
@@ -4893,16 +4721,16 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>464</v>
+        <v>404</v>
       </c>
       <c r="C163" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D163" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E163">
         <v>26980</v>
@@ -4910,16 +4738,16 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="C164" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D164" t="s">
-        <v>46</v>
+        <v>507</v>
       </c>
       <c r="E164">
         <v>5000</v>
@@ -4927,16 +4755,16 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>223</v>
+        <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>526</v>
+        <v>466</v>
       </c>
       <c r="C165" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D165" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E165">
         <v>25372</v>
@@ -4944,16 +4772,16 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>224</v>
+        <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>527</v>
+        <v>467</v>
       </c>
       <c r="C166" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D166" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E166">
         <v>30000</v>
@@ -4961,16 +4789,16 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="C167" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D167" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E167">
         <v>30976</v>
@@ -4978,16 +4806,16 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>466</v>
+        <v>406</v>
       </c>
       <c r="C168" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="D168" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E168">
         <v>5800</v>
@@ -4995,30 +4823,30 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="C169" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D169" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="C170" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D170" t="s">
-        <v>35</v>
+        <v>509</v>
       </c>
       <c r="E170">
         <v>17711</v>
@@ -5026,16 +4854,16 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>229</v>
+        <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="C171" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D171" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5043,16 +4871,16 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>462</v>
+        <v>402</v>
       </c>
       <c r="C172" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D172" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E172">
         <v>5895</v>
@@ -5060,16 +4888,16 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>231</v>
+        <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>529</v>
+        <v>469</v>
       </c>
       <c r="C173" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D173" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E173">
         <v>5000</v>
@@ -5077,16 +4905,16 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>506</v>
+        <v>446</v>
       </c>
       <c r="C174" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D174" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E174">
         <v>127625</v>
@@ -5094,16 +4922,16 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>233</v>
+        <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>530</v>
+        <v>470</v>
       </c>
       <c r="C175" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D175" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E175">
         <v>31999</v>
@@ -5111,16 +4939,16 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>234</v>
+        <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>531</v>
+        <v>471</v>
       </c>
       <c r="C176" t="s">
+        <v>443</v>
+      </c>
+      <c r="D176" t="s">
         <v>503</v>
-      </c>
-      <c r="D176" t="s">
-        <v>47</v>
       </c>
       <c r="E176">
         <v>30999</v>
@@ -5128,16 +4956,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>235</v>
+        <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>509</v>
+        <v>449</v>
       </c>
       <c r="C177" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E177">
         <v>30929</v>
@@ -5145,16 +4973,16 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>507</v>
+        <v>447</v>
       </c>
       <c r="C178" t="s">
-        <v>508</v>
+        <v>448</v>
       </c>
       <c r="D178" t="s">
-        <v>48</v>
+        <v>503</v>
       </c>
       <c r="E178">
         <v>29990</v>
@@ -5162,16 +4990,16 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>237</v>
+        <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>473</v>
+        <v>413</v>
       </c>
       <c r="C179" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D179" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E179">
         <v>24634</v>
@@ -5179,16 +5007,16 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="C180" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D180" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E180">
         <v>23276</v>
@@ -5196,16 +5024,16 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="C181" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D181" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E181">
         <v>28285</v>
@@ -5213,16 +5041,16 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>449</v>
+        <v>389</v>
       </c>
       <c r="C182" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D182" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E182">
         <v>30358</v>
@@ -5230,16 +5058,16 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="C183" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D183" t="s">
-        <v>41</v>
+        <v>508</v>
       </c>
       <c r="E183">
         <v>29990</v>
@@ -5247,16 +5075,16 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="C184" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D184" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E184">
         <v>139315</v>
@@ -5264,16 +5092,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>491</v>
+        <v>431</v>
       </c>
       <c r="C185" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D185" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E185">
         <v>25993</v>
@@ -5281,30 +5109,30 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="C186" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D186" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>442</v>
+        <v>382</v>
       </c>
       <c r="C187" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D187" t="s">
-        <v>47</v>
+        <v>503</v>
       </c>
       <c r="E187">
         <v>30281</v>
@@ -5312,16 +5140,16 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>425</v>
+        <v>365</v>
       </c>
       <c r="C188" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D188" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E188">
         <v>26500</v>
@@ -5329,16 +5157,16 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="C189" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D189" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E189">
         <v>30000</v>
@@ -5346,16 +5174,16 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="C190" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D190" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E190">
         <v>11434</v>
@@ -5363,16 +5191,16 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="C191" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D191" t="s">
-        <v>36</v>
+        <v>506</v>
       </c>
       <c r="E191">
         <v>25063</v>
@@ -5380,16 +5208,16 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>481</v>
+        <v>421</v>
       </c>
       <c r="C192" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D192" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E192">
         <v>25826</v>
@@ -5397,16 +5225,16 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>251</v>
+        <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="C193" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D193" t="s">
-        <v>33</v>
+        <v>507</v>
       </c>
       <c r="E193">
         <v>4626</v>
@@ -5414,16 +5242,16 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>252</v>
+        <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>455</v>
+        <v>395</v>
       </c>
       <c r="C194" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D194" t="s">
-        <v>41</v>
+        <v>508</v>
       </c>
       <c r="E194">
         <v>25702</v>
@@ -5431,16 +5259,16 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>253</v>
+        <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>532</v>
+        <v>472</v>
       </c>
       <c r="C195" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D195" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E195">
         <v>25680</v>
@@ -5448,16 +5276,16 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>254</v>
+        <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>456</v>
+        <v>396</v>
       </c>
       <c r="C196" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D196" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E196">
         <v>139886</v>
@@ -5465,16 +5293,16 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>255</v>
+        <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C197" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D197" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -5482,16 +5310,16 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>533</v>
+        <v>473</v>
       </c>
       <c r="C198" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D198" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E198">
         <v>31427</v>
@@ -5499,16 +5327,16 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
       <c r="C199" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D199" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E199">
         <v>29292</v>
@@ -5516,16 +5344,16 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>258</v>
+        <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="C200" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D200" t="s">
-        <v>8</v>
+        <v>505</v>
       </c>
       <c r="E200">
         <v>10718</v>
@@ -5533,16 +5361,16 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>259</v>
+        <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>427</v>
+        <v>367</v>
       </c>
       <c r="C201" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="D201" t="s">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="E201">
         <v>15993</v>
@@ -5550,16 +5378,16 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>498</v>
+        <v>438</v>
       </c>
       <c r="C202" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D202" t="s">
-        <v>3</v>
+        <v>503</v>
       </c>
       <c r="E202">
         <v>29900</v>
@@ -5567,16 +5395,16 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>464</v>
+        <v>404</v>
       </c>
       <c r="C203" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D203" t="s">
-        <v>49</v>
+        <v>506</v>
       </c>
       <c r="E203">
         <v>27696</v>
@@ -5584,16 +5412,16 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>262</v>
+        <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
       <c r="C204" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D204" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E204">
         <v>31202</v>
@@ -5601,16 +5429,16 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>263</v>
+        <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>535</v>
+        <v>475</v>
       </c>
       <c r="C205" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D205" t="s">
-        <v>20</v>
+        <v>503</v>
       </c>
       <c r="E205">
         <v>15579</v>
@@ -5618,16 +5446,16 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>536</v>
+        <v>476</v>
       </c>
       <c r="C206" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D206" t="s">
-        <v>19</v>
+        <v>504</v>
       </c>
       <c r="E206">
         <v>124464</v>
@@ -5635,16 +5463,16 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>265</v>
+        <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>537</v>
+        <v>477</v>
       </c>
       <c r="C207" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D207" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -5652,16 +5480,16 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>538</v>
+        <v>478</v>
       </c>
       <c r="C208" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D208" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E208">
         <v>145900</v>
@@ -5669,16 +5497,16 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C209" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D209" t="s">
-        <v>22</v>
+        <v>505</v>
       </c>
       <c r="E209">
         <v>9134</v>
@@ -5686,16 +5514,16 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
       <c r="C210" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D210" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -5703,16 +5531,16 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>269</v>
+        <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="C211" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D211" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -5720,16 +5548,16 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>459</v>
+        <v>399</v>
       </c>
       <c r="C212" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D212" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E212">
         <v>32320</v>
@@ -5737,16 +5565,16 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>271</v>
+        <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="C213" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D213" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E213">
         <v>30581</v>
@@ -5754,16 +5582,16 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>539</v>
+        <v>479</v>
       </c>
       <c r="C214" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D214" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -5771,16 +5599,16 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>273</v>
+        <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>452</v>
+        <v>392</v>
       </c>
       <c r="C215" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D215" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E215">
         <v>30000</v>
@@ -5788,16 +5616,16 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>274</v>
+        <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>473</v>
+        <v>413</v>
       </c>
       <c r="C216" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="D216" t="s">
-        <v>50</v>
+        <v>502</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -5805,16 +5633,16 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C217" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D217" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E217">
         <v>29097</v>
@@ -5822,16 +5650,16 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="C218" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D218" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E218">
         <v>22071</v>
@@ -5839,16 +5667,16 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>277</v>
+        <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="C219" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D219" t="s">
-        <v>3</v>
+        <v>503</v>
       </c>
       <c r="E219">
         <v>25089</v>
@@ -5856,16 +5684,16 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>278</v>
+        <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>541</v>
+        <v>481</v>
       </c>
       <c r="C220" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D220" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E220">
         <v>24248</v>
@@ -5873,16 +5701,16 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>279</v>
+        <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>479</v>
+        <v>419</v>
       </c>
       <c r="C221" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D221" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E221">
         <v>25698</v>
@@ -5890,16 +5718,16 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="C222" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D222" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E222">
         <v>101635</v>
@@ -5907,16 +5735,16 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>476</v>
+        <v>416</v>
       </c>
       <c r="C223" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D223" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E223">
         <v>128539</v>
@@ -5924,16 +5752,16 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C224" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D224" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -5941,16 +5769,16 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>283</v>
+        <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>476</v>
+        <v>416</v>
       </c>
       <c r="C225" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D225" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E225">
         <v>130374</v>
@@ -5958,16 +5786,16 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C226" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D226" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E226">
         <v>117306</v>
@@ -5975,16 +5803,16 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>425</v>
+        <v>365</v>
       </c>
       <c r="C227" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D227" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E227">
         <v>5386</v>
@@ -5992,16 +5820,16 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>286</v>
+        <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>467</v>
+        <v>407</v>
       </c>
       <c r="C228" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D228" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E228">
         <v>125566</v>
@@ -6009,16 +5837,16 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>287</v>
+        <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>542</v>
+        <v>482</v>
       </c>
       <c r="C229" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E229">
         <v>30485</v>
@@ -6026,16 +5854,16 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>288</v>
+        <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>448</v>
+        <v>388</v>
       </c>
       <c r="C230" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D230" t="s">
-        <v>14</v>
+        <v>508</v>
       </c>
       <c r="E230">
         <v>30077</v>
@@ -6043,16 +5871,16 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="C231" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D231" t="s">
-        <v>35</v>
+        <v>509</v>
       </c>
       <c r="E231">
         <v>16710</v>
@@ -6060,16 +5888,16 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="C232" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D232" t="s">
-        <v>51</v>
+        <v>507</v>
       </c>
       <c r="E232">
         <v>10676</v>
@@ -6077,16 +5905,16 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>291</v>
+        <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C233" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D233" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E233">
         <v>25106</v>
@@ -6094,16 +5922,16 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>543</v>
+        <v>483</v>
       </c>
       <c r="C234" t="s">
-        <v>489</v>
+        <v>429</v>
       </c>
       <c r="D234" t="s">
-        <v>38</v>
+        <v>510</v>
       </c>
       <c r="E234">
         <v>29900</v>
@@ -6111,16 +5939,16 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>293</v>
+        <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>486</v>
+        <v>426</v>
       </c>
       <c r="C235" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D235" t="s">
-        <v>9</v>
+        <v>506</v>
       </c>
       <c r="E235">
         <v>16268</v>
@@ -6128,16 +5956,16 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>544</v>
+        <v>484</v>
       </c>
       <c r="C236" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D236" t="s">
-        <v>34</v>
+        <v>506</v>
       </c>
       <c r="E236">
         <v>25143</v>
@@ -6145,16 +5973,16 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>295</v>
+        <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>545</v>
+        <v>485</v>
       </c>
       <c r="C237" t="s">
-        <v>489</v>
+        <v>429</v>
       </c>
       <c r="D237" t="s">
-        <v>38</v>
+        <v>510</v>
       </c>
       <c r="E237">
         <v>29900</v>
@@ -6162,16 +5990,16 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="C238" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D238" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E238">
         <v>15707</v>
@@ -6179,16 +6007,16 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>418</v>
+        <v>358</v>
       </c>
       <c r="C239" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D239" t="s">
-        <v>52</v>
+        <v>503</v>
       </c>
       <c r="E239">
         <v>29986</v>
@@ -6196,16 +6024,16 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>467</v>
+        <v>407</v>
       </c>
       <c r="C240" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D240" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E240">
         <v>5500</v>
@@ -6213,16 +6041,16 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="C241" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D241" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E241">
         <v>25435</v>
@@ -6230,16 +6058,16 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>456</v>
+        <v>396</v>
       </c>
       <c r="C242" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D242" t="s">
-        <v>25</v>
+        <v>505</v>
       </c>
       <c r="E242">
         <v>22494</v>
@@ -6247,16 +6075,16 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C243" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D243" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E243">
         <v>32777</v>
@@ -6264,16 +6092,16 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>431</v>
+        <v>371</v>
       </c>
       <c r="C244" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D244" t="s">
-        <v>51</v>
+        <v>507</v>
       </c>
       <c r="E244">
         <v>10143</v>
@@ -6281,16 +6109,16 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>485</v>
+        <v>425</v>
       </c>
       <c r="C245" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D245" t="s">
-        <v>53</v>
+        <v>503</v>
       </c>
       <c r="E245">
         <v>30443</v>
@@ -6298,16 +6126,16 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>546</v>
+        <v>486</v>
       </c>
       <c r="C246" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D246" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -6315,16 +6143,16 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>305</v>
+        <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C247" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D247" t="s">
-        <v>26</v>
+        <v>506</v>
       </c>
       <c r="E247">
         <v>15980</v>
@@ -6332,16 +6160,16 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C248" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D248" t="s">
-        <v>49</v>
+        <v>506</v>
       </c>
       <c r="E248">
         <v>27989</v>
@@ -6349,16 +6177,16 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="C249" t="s">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="D249" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -6366,16 +6194,16 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="C250" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D250" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E250">
         <v>30000</v>
@@ -6383,16 +6211,16 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>493</v>
+        <v>433</v>
       </c>
       <c r="C251" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D251" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E251">
         <v>27835</v>
@@ -6400,16 +6228,16 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="C252" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D252" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E252">
         <v>29997</v>
@@ -6417,16 +6245,16 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>311</v>
+        <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="C253" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D253" t="s">
-        <v>34</v>
+        <v>506</v>
       </c>
       <c r="E253">
         <v>19267</v>
@@ -6434,16 +6262,16 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="C254" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D254" t="s">
-        <v>49</v>
+        <v>506</v>
       </c>
       <c r="E254">
         <v>25983</v>
@@ -6451,16 +6279,16 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>313</v>
+        <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>436</v>
+        <v>376</v>
       </c>
       <c r="C255" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D255" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E255">
         <v>6695</v>
@@ -6468,16 +6296,16 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>512</v>
+        <v>452</v>
       </c>
       <c r="C256" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D256" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -6485,16 +6313,16 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>531</v>
+        <v>471</v>
       </c>
       <c r="C257" t="s">
+        <v>443</v>
+      </c>
+      <c r="D257" t="s">
         <v>503</v>
-      </c>
-      <c r="D257" t="s">
-        <v>12</v>
       </c>
       <c r="E257">
         <v>16999</v>
@@ -6502,16 +6330,16 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>316</v>
+        <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>506</v>
+        <v>446</v>
       </c>
       <c r="C258" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D258" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E258">
         <v>25999</v>
@@ -6519,16 +6347,16 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>317</v>
+        <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>519</v>
+        <v>459</v>
       </c>
       <c r="C259" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D259" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E259">
         <v>4864</v>
@@ -6536,16 +6364,16 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>547</v>
+        <v>487</v>
       </c>
       <c r="C260" t="s">
-        <v>508</v>
+        <v>448</v>
       </c>
       <c r="D260" t="s">
-        <v>8</v>
+        <v>505</v>
       </c>
       <c r="E260">
         <v>11990</v>
@@ -6553,16 +6381,16 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>530</v>
+        <v>470</v>
       </c>
       <c r="C261" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D261" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -6570,16 +6398,16 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>548</v>
+        <v>488</v>
       </c>
       <c r="C262" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D262" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E262">
         <v>129946</v>
@@ -6587,16 +6415,16 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>321</v>
+        <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C263" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D263" t="s">
-        <v>46</v>
+        <v>507</v>
       </c>
       <c r="E263">
         <v>16237</v>
@@ -6604,16 +6432,16 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>461</v>
+        <v>401</v>
       </c>
       <c r="C264" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D264" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E264">
         <v>128531</v>
@@ -6621,16 +6449,16 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>323</v>
+        <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="C265" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D265" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E265">
         <v>6900</v>
@@ -6638,16 +6466,16 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C266" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D266" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E266">
         <v>25943</v>
@@ -6655,16 +6483,16 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>325</v>
+        <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>549</v>
+        <v>489</v>
       </c>
       <c r="C267" t="s">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="D267" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -6672,16 +6500,16 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="C268" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D268" t="s">
-        <v>17</v>
+        <v>503</v>
       </c>
       <c r="E268">
         <v>16990</v>
@@ -6689,30 +6517,30 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>327</v>
+        <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>466</v>
+        <v>406</v>
       </c>
       <c r="C269" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="D269" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>550</v>
+        <v>490</v>
       </c>
       <c r="C270" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="D270" t="s">
-        <v>54</v>
+        <v>507</v>
       </c>
       <c r="E270">
         <v>5900</v>
@@ -6720,16 +6548,16 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>329</v>
+        <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="C271" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D271" t="s">
-        <v>11</v>
+        <v>507</v>
       </c>
       <c r="E271">
         <v>14123</v>
@@ -6737,16 +6565,16 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>448</v>
+        <v>388</v>
       </c>
       <c r="C272" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D272" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -6754,16 +6582,16 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>331</v>
+        <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
       <c r="C273" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D273" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E273">
         <v>32490</v>
@@ -6771,16 +6599,16 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>332</v>
+        <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>532</v>
+        <v>472</v>
       </c>
       <c r="C274" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D274" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E274">
         <v>30267</v>
@@ -6788,16 +6616,16 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>333</v>
+        <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C275" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D275" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E275">
         <v>119097</v>
@@ -6805,16 +6633,16 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>334</v>
+        <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="C276" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D276" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E276">
         <v>25829</v>
@@ -6822,16 +6650,16 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>335</v>
+        <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>532</v>
+        <v>472</v>
       </c>
       <c r="C277" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D277" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E277">
         <v>25789</v>
@@ -6839,16 +6667,16 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>336</v>
+        <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="C278" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D278" t="s">
-        <v>36</v>
+        <v>506</v>
       </c>
       <c r="E278">
         <v>26571</v>
@@ -6856,16 +6684,16 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>337</v>
+        <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="C279" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D279" t="s">
-        <v>44</v>
+        <v>506</v>
       </c>
       <c r="E279">
         <v>15995</v>
@@ -6873,16 +6701,16 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>338</v>
+        <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>546</v>
+        <v>486</v>
       </c>
       <c r="C280" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D280" t="s">
-        <v>55</v>
+        <v>507</v>
       </c>
       <c r="E280">
         <v>6900</v>
@@ -6890,16 +6718,16 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>339</v>
+        <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C281" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D281" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -6907,16 +6735,16 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="C282" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D282" t="s">
-        <v>56</v>
+        <v>507</v>
       </c>
       <c r="E282">
         <v>65058</v>
@@ -6924,16 +6752,16 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>341</v>
+        <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>498</v>
+        <v>438</v>
       </c>
       <c r="C283" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D283" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E283">
         <v>6900</v>
@@ -6941,16 +6769,16 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>342</v>
+        <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="C284" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D284" t="s">
-        <v>33</v>
+        <v>507</v>
       </c>
       <c r="E284">
         <v>5000</v>
@@ -6958,16 +6786,16 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>343</v>
+        <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="C285" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D285" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E285">
         <v>151000</v>
@@ -6975,16 +6803,16 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>344</v>
+        <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C286" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D286" t="s">
-        <v>35</v>
+        <v>509</v>
       </c>
       <c r="E286">
         <v>15988</v>
@@ -6992,16 +6820,16 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>345</v>
+        <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>542</v>
+        <v>482</v>
       </c>
       <c r="C287" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D287" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E287">
         <v>29980</v>
@@ -7009,16 +6837,16 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>346</v>
+        <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>551</v>
+        <v>491</v>
       </c>
       <c r="C288" t="s">
-        <v>424</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>57</v>
+        <v>364</v>
+      </c>
+      <c r="D288" t="s">
+        <v>502</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -7026,16 +6854,16 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>347</v>
+        <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>486</v>
+        <v>426</v>
       </c>
       <c r="C289" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D289" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E289">
         <v>158499</v>
@@ -7043,16 +6871,16 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>348</v>
+        <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>542</v>
+        <v>482</v>
       </c>
       <c r="C290" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D290" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -7060,16 +6888,16 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>349</v>
+        <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>448</v>
+        <v>388</v>
       </c>
       <c r="C291" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D291" t="s">
-        <v>19</v>
+        <v>504</v>
       </c>
       <c r="E291">
         <v>140956</v>
@@ -7077,16 +6905,16 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>467</v>
+        <v>407</v>
       </c>
       <c r="C292" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D292" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E292">
         <v>120564</v>
@@ -7094,16 +6922,16 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>351</v>
+        <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>483</v>
+        <v>423</v>
       </c>
       <c r="C293" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D293" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E293">
         <v>5383</v>
@@ -7111,16 +6939,16 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>352</v>
+        <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>551</v>
+        <v>491</v>
       </c>
       <c r="C294" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D294" t="s">
-        <v>28</v>
+        <v>502</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -7128,16 +6956,16 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>414</v>
+        <v>354</v>
       </c>
       <c r="C295" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D295" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -7145,16 +6973,16 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>354</v>
+        <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>462</v>
+        <v>402</v>
       </c>
       <c r="C296" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D296" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E296">
         <v>22917</v>
@@ -7162,16 +6990,16 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>355</v>
+        <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>486</v>
+        <v>426</v>
       </c>
       <c r="C297" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D297" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E297">
         <v>27900</v>
@@ -7179,16 +7007,16 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>356</v>
+        <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
       <c r="C298" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D298" t="s">
-        <v>1</v>
+        <v>508</v>
       </c>
       <c r="E298">
         <v>32990</v>
@@ -7196,16 +7024,16 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>357</v>
+        <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="C299" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D299" t="s">
-        <v>22</v>
+        <v>505</v>
       </c>
       <c r="E299">
         <v>6307</v>
@@ -7213,16 +7041,16 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="C300" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D300" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E300">
         <v>5770</v>
@@ -7230,16 +7058,16 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>359</v>
+        <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="C301" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D301" t="s">
-        <v>34</v>
+        <v>506</v>
       </c>
       <c r="E301">
         <v>17672</v>
@@ -7247,16 +7075,16 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="C302" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D302" t="s">
-        <v>35</v>
+        <v>509</v>
       </c>
       <c r="E302">
         <v>16610</v>
@@ -7264,16 +7092,16 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>361</v>
+        <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>552</v>
+        <v>492</v>
       </c>
       <c r="C303" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D303" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E303">
         <v>24993</v>
@@ -7281,16 +7109,16 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>362</v>
+        <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>529</v>
+        <v>469</v>
       </c>
       <c r="C304" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D304" t="s">
-        <v>34</v>
+        <v>506</v>
       </c>
       <c r="E304">
         <v>15840</v>
@@ -7298,16 +7126,16 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>363</v>
+        <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>449</v>
+        <v>389</v>
       </c>
       <c r="C305" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D305" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="E305">
         <v>14900</v>
@@ -7315,16 +7143,16 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>364</v>
+        <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>479</v>
+        <v>419</v>
       </c>
       <c r="C306" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D306" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E306">
         <v>5000</v>
@@ -7332,16 +7160,16 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>365</v>
+        <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>478</v>
+        <v>418</v>
       </c>
       <c r="C307" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D307" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E307">
         <v>116062</v>
@@ -7349,16 +7177,16 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>478</v>
+        <v>418</v>
       </c>
       <c r="C308" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D308" t="s">
-        <v>16</v>
+        <v>508</v>
       </c>
       <c r="E308">
         <v>32508</v>
@@ -7366,16 +7194,16 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>367</v>
+        <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>479</v>
+        <v>419</v>
       </c>
       <c r="C309" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D309" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -7383,16 +7211,16 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>368</v>
+        <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>476</v>
+        <v>416</v>
       </c>
       <c r="C310" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="D310" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E310">
         <v>1654</v>
@@ -7400,16 +7228,16 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>369</v>
+        <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>549</v>
+        <v>489</v>
       </c>
       <c r="C311" t="s">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="D311" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E311">
         <v>27900</v>
@@ -7417,16 +7245,16 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C312" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D312" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E312">
         <v>165488</v>
@@ -7434,16 +7262,16 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>371</v>
+        <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="C313" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="D313" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E313">
         <v>159438</v>
@@ -7451,16 +7279,16 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>372</v>
+        <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="C314" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D314" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E314">
         <v>26034</v>
@@ -7468,16 +7296,16 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>373</v>
+        <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>553</v>
+        <v>493</v>
       </c>
       <c r="C315" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D315" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E315">
         <v>5843</v>
@@ -7485,16 +7313,16 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>374</v>
+        <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="C316" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D316" t="s">
-        <v>33</v>
+        <v>507</v>
       </c>
       <c r="E316">
         <v>6980</v>
@@ -7502,16 +7330,16 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>375</v>
+        <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
       <c r="C317" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D317" t="s">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -7519,16 +7347,16 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>376</v>
+        <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>433</v>
+        <v>373</v>
       </c>
       <c r="C318" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D318" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E318">
         <v>135211</v>
@@ -7536,16 +7364,16 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>455</v>
+        <v>395</v>
       </c>
       <c r="C319" t="s">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="D319" t="s">
-        <v>13</v>
+        <v>504</v>
       </c>
       <c r="E319">
         <v>135211</v>
@@ -7553,16 +7381,16 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="C320" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="D320" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E320">
         <v>30791</v>
@@ -7570,16 +7398,16 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>379</v>
+        <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="C321" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="D321" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E321">
         <v>24536</v>
@@ -7587,16 +7415,16 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>518</v>
+        <v>458</v>
       </c>
       <c r="C322" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D322" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E322">
         <v>5838</v>
@@ -7604,16 +7432,16 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>381</v>
+        <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="C323" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="D323" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E323">
         <v>5000</v>
@@ -7621,16 +7449,16 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>512</v>
+        <v>452</v>
       </c>
       <c r="C324" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D324" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -7638,16 +7466,16 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>383</v>
+        <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>518</v>
+        <v>458</v>
       </c>
       <c r="C325" t="s">
-        <v>513</v>
+        <v>453</v>
       </c>
       <c r="D325" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E325">
         <v>6254</v>
@@ -7655,16 +7483,16 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>384</v>
+        <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>506</v>
+        <v>446</v>
       </c>
       <c r="C326" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D326" t="s">
-        <v>30</v>
+        <v>511</v>
       </c>
       <c r="E326">
         <v>29999</v>
@@ -7672,16 +7500,16 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>385</v>
+        <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>530</v>
+        <v>470</v>
       </c>
       <c r="C327" t="s">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="D327" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E327">
         <v>27999</v>
@@ -7689,16 +7517,16 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>386</v>
+        <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>547</v>
+        <v>487</v>
       </c>
       <c r="C328" t="s">
+        <v>448</v>
+      </c>
+      <c r="D328" t="s">
         <v>508</v>
-      </c>
-      <c r="D328" t="s">
-        <v>16</v>
       </c>
       <c r="E328">
         <v>32900</v>
@@ -7706,16 +7534,16 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>387</v>
+        <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>499</v>
+        <v>439</v>
       </c>
       <c r="C329" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D329" t="s">
-        <v>27</v>
+        <v>507</v>
       </c>
       <c r="E329">
         <v>6900</v>
@@ -7723,16 +7551,16 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>388</v>
+        <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>554</v>
+        <v>494</v>
       </c>
       <c r="C330" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D330" t="s">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E330">
         <v>17000</v>
@@ -7740,16 +7568,16 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>389</v>
+        <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="C331" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D331" t="s">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E331">
         <v>16998</v>
@@ -7757,16 +7585,16 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>444</v>
+        <v>384</v>
       </c>
       <c r="C332" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D332" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E332">
         <v>27625</v>
@@ -7774,16 +7602,16 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>391</v>
+        <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>466</v>
+        <v>406</v>
       </c>
       <c r="C333" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D333" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -7791,16 +7619,16 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>392</v>
+        <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>425</v>
+        <v>365</v>
       </c>
       <c r="C334" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D334" t="s">
-        <v>58</v>
+        <v>507</v>
       </c>
       <c r="E334">
         <v>6459</v>
@@ -7808,16 +7636,16 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>393</v>
+        <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>436</v>
+        <v>376</v>
       </c>
       <c r="C335" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D335" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E335">
         <v>169000</v>
@@ -7825,16 +7653,16 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>394</v>
+        <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>471</v>
+        <v>411</v>
       </c>
       <c r="C336" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="D336" t="s">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E336">
         <v>15998</v>
@@ -7842,16 +7670,16 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>395</v>
+        <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>555</v>
+        <v>495</v>
       </c>
       <c r="C337" t="s">
-        <v>556</v>
+        <v>496</v>
       </c>
       <c r="D337" t="s">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="E337">
         <v>105681</v>
@@ -7859,30 +7687,30 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>396</v>
+        <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>529</v>
+        <v>469</v>
       </c>
       <c r="C338" t="s">
-        <v>556</v>
+        <v>496</v>
       </c>
       <c r="D338" t="s">
-        <v>28</v>
+        <v>502</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>397</v>
+        <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="C339" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="D339" t="s">
-        <v>59</v>
+        <v>503</v>
       </c>
       <c r="E339">
         <v>17423</v>
@@ -7890,16 +7718,16 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>398</v>
+        <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>544</v>
+        <v>484</v>
       </c>
       <c r="C340" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="D340" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E340">
         <v>26559</v>
@@ -7907,16 +7735,16 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>399</v>
+        <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>467</v>
+        <v>407</v>
       </c>
       <c r="C341" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D341" t="s">
-        <v>1</v>
+        <v>508</v>
       </c>
       <c r="E341">
         <v>29910</v>
@@ -7924,16 +7752,16 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C342" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D342" t="s">
-        <v>32</v>
+        <v>506</v>
       </c>
       <c r="E342">
         <v>29135</v>
@@ -7941,16 +7769,16 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>401</v>
+        <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>425</v>
+        <v>365</v>
       </c>
       <c r="C343" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D343" t="s">
-        <v>18</v>
+        <v>507</v>
       </c>
       <c r="E343">
         <v>5688</v>
@@ -7958,16 +7786,16 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>402</v>
+        <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="C344" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D344" t="s">
-        <v>6</v>
+        <v>505</v>
       </c>
       <c r="E344">
         <v>31169</v>
@@ -7975,16 +7803,16 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>403</v>
+        <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="C345" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D345" t="s">
-        <v>6</v>
+        <v>505</v>
       </c>
       <c r="E345">
         <v>31169</v>
@@ -7992,16 +7820,16 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>499</v>
+        <v>439</v>
       </c>
       <c r="C346" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="D346" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="E346">
         <v>26748</v>
@@ -8009,16 +7837,16 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>405</v>
+        <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="C347" t="s">
-        <v>496</v>
+        <v>436</v>
       </c>
       <c r="D347" t="s">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E347">
         <v>17000</v>
@@ -8026,16 +7854,16 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>406</v>
+        <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="C348" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="D348" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E348">
         <v>32521</v>
@@ -8043,16 +7871,16 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>407</v>
+        <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
       <c r="C349" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D349" t="s">
-        <v>10</v>
+        <v>508</v>
       </c>
       <c r="E349">
         <v>27900</v>
@@ -8060,16 +7888,16 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>408</v>
+        <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>466</v>
+        <v>406</v>
       </c>
       <c r="C350" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D350" t="s">
-        <v>35</v>
+        <v>509</v>
       </c>
       <c r="E350">
         <v>16990</v>
@@ -8077,16 +7905,16 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>409</v>
+        <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>538</v>
+        <v>478</v>
       </c>
       <c r="C351" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D351" t="s">
-        <v>49</v>
+        <v>506</v>
       </c>
       <c r="E351">
         <v>26957</v>
@@ -8094,16 +7922,16 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>410</v>
+        <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>466</v>
+        <v>406</v>
       </c>
       <c r="C352" t="s">
-        <v>465</v>
+        <v>405</v>
       </c>
       <c r="D352" t="s">
-        <v>25</v>
+        <v>505</v>
       </c>
       <c r="E352">
         <v>26780</v>
@@ -8111,16 +7939,16 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>411</v>
+        <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C353" t="s">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="D353" t="s">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="E353">
         <v>0</v>
@@ -8128,16 +7956,16 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>412</v>
+        <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>467</v>
+        <v>407</v>
       </c>
       <c r="C354" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="D354" t="s">
-        <v>5</v>
+        <v>504</v>
       </c>
       <c r="E354">
         <v>165804</v>
@@ -8145,16 +7973,16 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>413</v>
+        <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>538</v>
+        <v>478</v>
       </c>
       <c r="C355" t="s">
-        <v>415</v>
+        <v>355</v>
       </c>
       <c r="D355" t="s">
-        <v>7</v>
+        <v>503</v>
       </c>
       <c r="E355">
         <v>31900</v>
